--- a/src/data/downloads/local_2014_2016_may_sakrebulo_by_election_20160522_data.xlsx
+++ b/src/data/downloads/local_2014_2016_may_sakrebulo_by_election_20160522_data.xlsx
@@ -356,7 +356,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-21T18:04:35.562Z</t>
+    <t>2026-05-22T15:27:24.647Z</t>
   </si>
   <si>
     <t>Data Source</t>

--- a/src/data/downloads/local_2014_2016_may_sakrebulo_by_election_20160522_data.xlsx
+++ b/src/data/downloads/local_2014_2016_may_sakrebulo_by_election_20160522_data.xlsx
@@ -356,7 +356,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-22T15:27:24.647Z</t>
+    <t>2026-05-22T15:52:44.832Z</t>
   </si>
   <si>
     <t>Data Source</t>

--- a/src/data/downloads/local_2014_2016_may_sakrebulo_by_election_20160522_data.xlsx
+++ b/src/data/downloads/local_2014_2016_may_sakrebulo_by_election_20160522_data.xlsx
@@ -356,7 +356,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-22T15:52:44.832Z</t>
+    <t>2026-05-24T22:28:17.950Z</t>
   </si>
   <si>
     <t>Data Source</t>

--- a/src/data/downloads/local_2014_2016_may_sakrebulo_by_election_20160522_data.xlsx
+++ b/src/data/downloads/local_2014_2016_may_sakrebulo_by_election_20160522_data.xlsx
@@ -356,7 +356,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-24T22:28:17.950Z</t>
+    <t>2026-05-25T13:08:48.807Z</t>
   </si>
   <si>
     <t>Data Source</t>

--- a/src/data/downloads/local_2014_2016_may_sakrebulo_by_election_20160522_data.xlsx
+++ b/src/data/downloads/local_2014_2016_may_sakrebulo_by_election_20160522_data.xlsx
@@ -356,7 +356,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-25T13:08:48.807Z</t>
+    <t>2026-06-13T11:36:45.147Z</t>
   </si>
   <si>
     <t>Data Source</t>
@@ -3303,7 +3303,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -10667,7 +10667,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -13185,7 +13185,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -20549,7 +20549,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
